--- a/data/sources/countries/el_salvador.xlsx
+++ b/data/sources/countries/el_salvador.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,23 +25,13 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="9"/>
-    </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="001F3864"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -58,9 +48,7 @@
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -426,377 +414,288 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI7"/>
+  <dimension ref="A1:BD7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="24" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="38" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
-    <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="14" customWidth="1" min="14" max="14"/>
-    <col width="14" customWidth="1" min="15" max="15"/>
-    <col width="70" customWidth="1" min="16" max="16"/>
-    <col width="70" customWidth="1" min="17" max="17"/>
-    <col width="26" customWidth="1" min="18" max="18"/>
-    <col width="14" customWidth="1" min="19" max="19"/>
-    <col width="14" customWidth="1" min="20" max="20"/>
-    <col width="14" customWidth="1" min="21" max="21"/>
-    <col width="14" customWidth="1" min="22" max="22"/>
-    <col width="14" customWidth="1" min="23" max="23"/>
-    <col width="14" customWidth="1" min="24" max="24"/>
-    <col width="14" customWidth="1" min="25" max="25"/>
-    <col width="14" customWidth="1" min="26" max="26"/>
-    <col width="14" customWidth="1" min="27" max="27"/>
-    <col width="14" customWidth="1" min="28" max="28"/>
-    <col width="14" customWidth="1" min="29" max="29"/>
-    <col width="14" customWidth="1" min="30" max="30"/>
-    <col width="14" customWidth="1" min="31" max="31"/>
-    <col width="14" customWidth="1" min="32" max="32"/>
-    <col width="14" customWidth="1" min="33" max="33"/>
-    <col width="14" customWidth="1" min="34" max="34"/>
-    <col width="14" customWidth="1" min="35" max="35"/>
-    <col width="14" customWidth="1" min="36" max="36"/>
-    <col width="14" customWidth="1" min="37" max="37"/>
-    <col width="14" customWidth="1" min="38" max="38"/>
-    <col width="14" customWidth="1" min="39" max="39"/>
-    <col width="14" customWidth="1" min="40" max="40"/>
-    <col width="14" customWidth="1" min="41" max="41"/>
-    <col width="14" customWidth="1" min="42" max="42"/>
-    <col width="14" customWidth="1" min="43" max="43"/>
-    <col width="14" customWidth="1" min="44" max="44"/>
-    <col width="14" customWidth="1" min="45" max="45"/>
-    <col width="14" customWidth="1" min="46" max="46"/>
-    <col width="14" customWidth="1" min="47" max="47"/>
-    <col width="14" customWidth="1" min="48" max="48"/>
-    <col width="14" customWidth="1" min="49" max="49"/>
-    <col width="14" customWidth="1" min="50" max="50"/>
-    <col width="14" customWidth="1" min="51" max="51"/>
-    <col width="14" customWidth="1" min="52" max="52"/>
-    <col width="14" customWidth="1" min="53" max="53"/>
-    <col width="14" customWidth="1" min="54" max="54"/>
-    <col width="80" customWidth="1" min="55" max="55"/>
-    <col width="14" customWidth="1" min="56" max="56"/>
-    <col width="26" customWidth="1" min="57" max="57"/>
-    <col width="14" customWidth="1" min="58" max="58"/>
-    <col width="14" customWidth="1" min="59" max="59"/>
-    <col width="14" customWidth="1" min="60" max="60"/>
-    <col width="14" customWidth="1" min="61" max="61"/>
-    <col width="14" customWidth="1" min="62" max="62"/>
-  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Id_Investment</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Id_Investment_Original</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Id_Seq</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Coordinates</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Country</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>COUNTRY_ISO_ALPHA3</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>COUNTRY_ISO_NUM</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Province_ISO</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Year</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Investor</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Vector</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Path</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Area_EN</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Area_ES</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Detail_ES</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Detail_EN</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Location</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Investment</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Joint_Venture</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Origin_Of_Seller</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>Stake</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>Project_Type</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>Research</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>News</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>Caso1</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>Link1</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>Caso2</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>Link2</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>Caso3</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>Link3</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>Caso4</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>Link4</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>Caso5</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>Link5</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>Caso6</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>Link6</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>Caso7</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>Link7</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AM1" t="inlineStr">
         <is>
           <t>Caso8</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AN1" t="inlineStr">
         <is>
           <t>Link8</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AO1" t="inlineStr">
         <is>
           <t>Caso9</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AP1" t="inlineStr">
         <is>
           <t>Link9</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="AQ1" t="inlineStr">
         <is>
           <t>Caso10</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="AR1" t="inlineStr">
         <is>
           <t>Link10</t>
         </is>
       </c>
-      <c r="AS1" s="1" t="inlineStr">
+      <c r="AS1" t="inlineStr">
         <is>
           <t>Caso11</t>
         </is>
       </c>
-      <c r="AT1" s="1" t="inlineStr">
+      <c r="AT1" t="inlineStr">
         <is>
           <t>Link11</t>
         </is>
       </c>
-      <c r="AU1" s="1" t="inlineStr">
+      <c r="AU1" t="inlineStr">
         <is>
           <t>Caso12</t>
         </is>
       </c>
-      <c r="AV1" s="1" t="inlineStr">
+      <c r="AV1" t="inlineStr">
         <is>
           <t>Link12</t>
         </is>
       </c>
-      <c r="AW1" s="1" t="inlineStr">
+      <c r="AW1" t="inlineStr">
         <is>
           <t>Caso13</t>
         </is>
       </c>
-      <c r="AX1" s="1" t="inlineStr">
+      <c r="AX1" t="inlineStr">
         <is>
           <t>Link13</t>
         </is>
       </c>
-      <c r="AY1" s="1" t="inlineStr">
+      <c r="AY1" t="inlineStr">
         <is>
           <t>Caso14</t>
         </is>
       </c>
-      <c r="AZ1" s="1" t="inlineStr">
+      <c r="AZ1" t="inlineStr">
         <is>
           <t>Link14</t>
         </is>
       </c>
-      <c r="BA1" s="1" t="inlineStr">
+      <c r="BA1" t="inlineStr">
         <is>
           <t>reliability_score</t>
         </is>
       </c>
-      <c r="BB1" s="1" t="inlineStr">
-        <is>
-          <t>reliability_notes</t>
-        </is>
-      </c>
-      <c r="BC1" s="1" t="inlineStr">
-        <is>
-          <t>cancelled</t>
-        </is>
-      </c>
-      <c r="BD1" s="1" t="inlineStr">
-        <is>
-          <t>cancelled_motivo</t>
-        </is>
-      </c>
-      <c r="BE1" s="1" t="inlineStr">
+      <c r="BB1" t="inlineStr">
         <is>
           <t>source1</t>
         </is>
       </c>
-      <c r="BF1" s="1" t="inlineStr">
+      <c r="BC1" t="inlineStr">
         <is>
           <t>source2</t>
         </is>
       </c>
-      <c r="BG1" s="1" t="inlineStr">
+      <c r="BD1" t="inlineStr">
         <is>
           <t>source3</t>
-        </is>
-      </c>
-      <c r="BH1" s="1" t="inlineStr">
-        <is>
-          <t>source4</t>
-        </is>
-      </c>
-      <c r="BI1" s="1" t="inlineStr">
-        <is>
-          <t>source5</t>
         </is>
       </c>
     </row>
@@ -824,7 +723,7 @@
           <t>SLV</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G2" s="1" t="inlineStr">
         <is>
           <t>222</t>
         </is>
@@ -839,7 +738,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Government of China</t>
+          <t>Gobierno de la Republica Popular China</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -893,20 +792,17 @@
       <c r="BA2" t="n">
         <v>3</v>
       </c>
-      <c r="BC2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE2" t="inlineStr">
+      <c r="BB2" t="inlineStr">
         <is>
           <t>https://www.elsalvador.com/noticias/nacional/inician-los-preparativos-para-la-construccion-de-cifco/1276219/2026/</t>
         </is>
       </c>
-      <c r="BF2" t="inlineStr">
+      <c r="BC2" t="inlineStr">
         <is>
           <t>https://www.laprensagrafica.com/elsalvador/Nuevo-Centro-Internacional-de-Ferias-y-Convenciones-se-construira-en-finca-El-Espino-20250711-0033.html</t>
         </is>
       </c>
-      <c r="BG2" t="inlineStr">
+      <c r="BD2" t="inlineStr">
         <is>
           <t>https://cifco.gob.sv/nuevo-cifco/</t>
         </is>
@@ -936,7 +832,7 @@
           <t>SLV</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G3" s="1" t="inlineStr">
         <is>
           <t>222</t>
         </is>
@@ -951,7 +847,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>PowerChina</t>
+          <t>Power Construction Corporation of China (PowerChina)</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1005,15 +901,12 @@
       <c r="BA3" t="n">
         <v>3</v>
       </c>
-      <c r="BC3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE3" t="inlineStr">
+      <c r="BB3" t="inlineStr">
         <is>
           <t>https://dialogo-americas.com/articles/china-strengthens-its-strategic-influence-in-el-salvadors-energy-sector/</t>
         </is>
       </c>
-      <c r="BF3" t="inlineStr">
+      <c r="BC3" t="inlineStr">
         <is>
           <t>https://prensamercosur.org/2026/06/26/china-refuerza-su-influencia-estrategica-en-la-energia-de-el-salvador/</t>
         </is>
@@ -1043,7 +936,7 @@
           <t>SLV</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G4" s="1" t="inlineStr">
         <is>
           <t>222</t>
         </is>
@@ -1058,7 +951,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>China Harbour Engineering Company</t>
+          <t>China Harbour Engineering Company (CHEC), filial de CCCC</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1115,20 +1008,17 @@
       <c r="BA4" t="n">
         <v>4</v>
       </c>
-      <c r="BC4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE4" t="inlineStr">
+      <c r="BB4" t="inlineStr">
         <is>
           <t>https://www.expedientepublico.org/muelle-turistico-en-el-salvador-us24-millones-de-secretos-en-inversion-china/</t>
         </is>
       </c>
-      <c r="BF4" t="inlineStr">
+      <c r="BC4" t="inlineStr">
         <is>
           <t>https://www.expedientepublico.org/el-salvador-y-china-megaobras-entre-secretismo-y-dano-ambiental/</t>
         </is>
       </c>
-      <c r="BG4" t="inlineStr">
+      <c r="BD4" t="inlineStr">
         <is>
           <t>https://es-us.noticias.yahoo.com/deportes/millonarias-obras-financiadas-china-salvador-144958591.html</t>
         </is>
@@ -1158,7 +1048,7 @@
           <t>SLV</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G5" s="1" t="inlineStr">
         <is>
           <t>222</t>
         </is>
@@ -1173,7 +1063,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Government of China</t>
+          <t>Gobierno de la Republica Popular China</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1230,20 +1120,17 @@
       <c r="BA5" t="n">
         <v>4</v>
       </c>
-      <c r="BC5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE5" t="inlineStr">
+      <c r="BB5" t="inlineStr">
         <is>
           <t>https://www.elsalvador.com/dinero-y-negocios/entorno-economico/china-el-salvador-cifco-estadios-de-futbol-planta-potabilizadora-ilopango/1276474/2026/</t>
         </is>
       </c>
-      <c r="BF5" t="inlineStr">
+      <c r="BC5" t="inlineStr">
         <is>
           <t>https://diariolahuella.com/china-sigue-dejando-huella-en-el-salvador-con-megaproyectos-historicos/</t>
         </is>
       </c>
-      <c r="BG5" t="inlineStr">
+      <c r="BD5" t="inlineStr">
         <is>
           <t>https://www.expedientepublico.org/el-salvador-y-china-megaobras-entre-secretismo-y-dano-ambiental/</t>
         </is>
@@ -1273,7 +1160,7 @@
           <t>SLV</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="G6" s="1" t="inlineStr">
         <is>
           <t>222</t>
         </is>
@@ -1288,7 +1175,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>China State Construction Engineering Corporation</t>
+          <t>China State Construction Engineering Corporation (CSCEC)</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1345,20 +1232,17 @@
       <c r="BA6" t="n">
         <v>5</v>
       </c>
-      <c r="BC6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE6" t="inlineStr">
+      <c r="BB6" t="inlineStr">
         <is>
           <t>https://www.revistaeyn.com/centroamericaymundo/este-sera-el-nuevo-estadio-nacional-de-el-salvador-donado-por-china-MF16467946</t>
         </is>
       </c>
-      <c r="BF6" t="inlineStr">
+      <c r="BC6" t="inlineStr">
         <is>
           <t>https://diario.elmundo.sv/politica/bukele-y-embajador-chino-colocan-primera-piedra-del-estadio-nacional</t>
         </is>
       </c>
-      <c r="BG6" t="inlineStr">
+      <c r="BD6" t="inlineStr">
         <is>
           <t>https://www.elimparcial.com/deporte/2025/12/23/el-salvador-tendra-un-mejor-estadio-que-el-azteca-en-2027-china-financia-el-megaproyecto-con-100-millones-de-dolares/</t>
         </is>
@@ -1388,7 +1272,7 @@
           <t>SLV</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G7" s="1" t="inlineStr">
         <is>
           <t>222</t>
         </is>
@@ -1460,20 +1344,17 @@
       <c r="BA7" t="n">
         <v>5</v>
       </c>
-      <c r="BC7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE7" t="inlineStr">
+      <c r="BB7" t="inlineStr">
         <is>
           <t>https://es-us.noticias.yahoo.com/deportes/millonarias-obras-financiadas-china-salvador-144958591.html</t>
         </is>
       </c>
-      <c r="BF7" t="inlineStr">
+      <c r="BC7" t="inlineStr">
         <is>
           <t>https://archivo.tiempo.hn/impresionante-asi-sera-la-biblioteca-nacional-de-el-salvador-construida-por-china/</t>
         </is>
       </c>
-      <c r="BG7" t="inlineStr">
+      <c r="BD7" t="inlineStr">
         <is>
           <t>https://nicasnews.com/2021/nueva-biblioteca-nacional-binaes/</t>
         </is>

--- a/data/sources/countries/el_salvador.xlsx
+++ b/data/sources/countries/el_salvador.xlsx
@@ -46,9 +46,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -414,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BD7"/>
+  <dimension ref="A1:BF7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -685,15 +684,25 @@
       </c>
       <c r="BB1" t="inlineStr">
         <is>
+          <t>reliability_notes</t>
+        </is>
+      </c>
+      <c r="BC1" t="inlineStr">
+        <is>
+          <t>cancelled_motivo</t>
+        </is>
+      </c>
+      <c r="BD1" t="inlineStr">
+        <is>
           <t>source1</t>
         </is>
       </c>
-      <c r="BC1" t="inlineStr">
+      <c r="BE1" t="inlineStr">
         <is>
           <t>source2</t>
         </is>
       </c>
-      <c r="BD1" t="inlineStr">
+      <c r="BF1" t="inlineStr">
         <is>
           <t>source3</t>
         </is>
@@ -705,6 +714,7 @@
           <t>SLV-0001</t>
         </is>
       </c>
+      <c r="B2" t="inlineStr"/>
       <c r="C2" t="n">
         <v>1</v>
       </c>
@@ -723,10 +733,8 @@
           <t>SLV</t>
         </is>
       </c>
-      <c r="G2" s="1" t="inlineStr">
-        <is>
-          <t>222</t>
-        </is>
+      <c r="G2" t="n">
+        <v>222</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -774,6 +782,10 @@
           <t>LA LIBERTAD</t>
         </is>
       </c>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
       <c r="V2" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -789,20 +801,50 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="inlineStr"/>
+      <c r="AB2" t="inlineStr"/>
+      <c r="AC2" t="inlineStr"/>
+      <c r="AD2" t="inlineStr"/>
+      <c r="AE2" t="inlineStr"/>
+      <c r="AF2" t="inlineStr"/>
+      <c r="AG2" t="inlineStr"/>
+      <c r="AH2" t="inlineStr"/>
+      <c r="AI2" t="inlineStr"/>
+      <c r="AJ2" t="inlineStr"/>
+      <c r="AK2" t="inlineStr"/>
+      <c r="AL2" t="inlineStr"/>
+      <c r="AM2" t="inlineStr"/>
+      <c r="AN2" t="inlineStr"/>
+      <c r="AO2" t="inlineStr"/>
+      <c r="AP2" t="inlineStr"/>
+      <c r="AQ2" t="inlineStr"/>
+      <c r="AR2" t="inlineStr"/>
+      <c r="AS2" t="inlineStr"/>
+      <c r="AT2" t="inlineStr"/>
+      <c r="AU2" t="inlineStr"/>
+      <c r="AV2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr"/>
+      <c r="AX2" t="inlineStr"/>
+      <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr"/>
       <c r="BA2" t="n">
         <v>3</v>
       </c>
-      <c r="BB2" t="inlineStr">
+      <c r="BB2" t="inlineStr"/>
+      <c r="BC2" t="inlineStr"/>
+      <c r="BD2" t="inlineStr">
         <is>
           <t>https://www.elsalvador.com/noticias/nacional/inician-los-preparativos-para-la-construccion-de-cifco/1276219/2026/</t>
         </is>
       </c>
-      <c r="BC2" t="inlineStr">
+      <c r="BE2" t="inlineStr">
         <is>
           <t>https://www.laprensagrafica.com/elsalvador/Nuevo-Centro-Internacional-de-Ferias-y-Convenciones-se-construira-en-finca-El-Espino-20250711-0033.html</t>
         </is>
       </c>
-      <c r="BD2" t="inlineStr">
+      <c r="BF2" t="inlineStr">
         <is>
           <t>https://cifco.gob.sv/nuevo-cifco/</t>
         </is>
@@ -814,6 +856,7 @@
           <t>SLV-0002</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
         <v>2</v>
       </c>
@@ -832,10 +875,8 @@
           <t>SLV</t>
         </is>
       </c>
-      <c r="G3" s="1" t="inlineStr">
-        <is>
-          <t>222</t>
-        </is>
+      <c r="G3" t="n">
+        <v>222</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -883,6 +924,10 @@
           <t>LA UNIÓN</t>
         </is>
       </c>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="inlineStr"/>
       <c r="V3" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -898,19 +943,50 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y3" t="inlineStr"/>
+      <c r="Z3" t="inlineStr"/>
+      <c r="AA3" t="inlineStr"/>
+      <c r="AB3" t="inlineStr"/>
+      <c r="AC3" t="inlineStr"/>
+      <c r="AD3" t="inlineStr"/>
+      <c r="AE3" t="inlineStr"/>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="inlineStr"/>
+      <c r="AH3" t="inlineStr"/>
+      <c r="AI3" t="inlineStr"/>
+      <c r="AJ3" t="inlineStr"/>
+      <c r="AK3" t="inlineStr"/>
+      <c r="AL3" t="inlineStr"/>
+      <c r="AM3" t="inlineStr"/>
+      <c r="AN3" t="inlineStr"/>
+      <c r="AO3" t="inlineStr"/>
+      <c r="AP3" t="inlineStr"/>
+      <c r="AQ3" t="inlineStr"/>
+      <c r="AR3" t="inlineStr"/>
+      <c r="AS3" t="inlineStr"/>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AU3" t="inlineStr"/>
+      <c r="AV3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr"/>
+      <c r="AX3" t="inlineStr"/>
+      <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr"/>
       <c r="BA3" t="n">
         <v>3</v>
       </c>
-      <c r="BB3" t="inlineStr">
+      <c r="BB3" t="inlineStr"/>
+      <c r="BC3" t="inlineStr"/>
+      <c r="BD3" t="inlineStr">
         <is>
           <t>https://dialogo-americas.com/articles/china-strengthens-its-strategic-influence-in-el-salvadors-energy-sector/</t>
         </is>
       </c>
-      <c r="BC3" t="inlineStr">
+      <c r="BE3" t="inlineStr">
         <is>
           <t>https://prensamercosur.org/2026/06/26/china-refuerza-su-influencia-estrategica-en-la-energia-de-el-salvador/</t>
         </is>
       </c>
+      <c r="BF3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -918,6 +994,7 @@
           <t>SLV-0003</t>
         </is>
       </c>
+      <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
         <v>3</v>
       </c>
@@ -936,10 +1013,8 @@
           <t>SLV</t>
         </is>
       </c>
-      <c r="G4" s="1" t="inlineStr">
-        <is>
-          <t>222</t>
-        </is>
+      <c r="G4" t="n">
+        <v>222</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -990,6 +1065,9 @@
       <c r="R4" t="n">
         <v>24</v>
       </c>
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr"/>
       <c r="V4" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -1005,20 +1083,50 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y4" t="inlineStr"/>
+      <c r="Z4" t="inlineStr"/>
+      <c r="AA4" t="inlineStr"/>
+      <c r="AB4" t="inlineStr"/>
+      <c r="AC4" t="inlineStr"/>
+      <c r="AD4" t="inlineStr"/>
+      <c r="AE4" t="inlineStr"/>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="inlineStr"/>
+      <c r="AH4" t="inlineStr"/>
+      <c r="AI4" t="inlineStr"/>
+      <c r="AJ4" t="inlineStr"/>
+      <c r="AK4" t="inlineStr"/>
+      <c r="AL4" t="inlineStr"/>
+      <c r="AM4" t="inlineStr"/>
+      <c r="AN4" t="inlineStr"/>
+      <c r="AO4" t="inlineStr"/>
+      <c r="AP4" t="inlineStr"/>
+      <c r="AQ4" t="inlineStr"/>
+      <c r="AR4" t="inlineStr"/>
+      <c r="AS4" t="inlineStr"/>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AU4" t="inlineStr"/>
+      <c r="AV4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr"/>
+      <c r="AX4" t="inlineStr"/>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr"/>
       <c r="BA4" t="n">
         <v>4</v>
       </c>
-      <c r="BB4" t="inlineStr">
+      <c r="BB4" t="inlineStr"/>
+      <c r="BC4" t="inlineStr"/>
+      <c r="BD4" t="inlineStr">
         <is>
           <t>https://www.expedientepublico.org/muelle-turistico-en-el-salvador-us24-millones-de-secretos-en-inversion-china/</t>
         </is>
       </c>
-      <c r="BC4" t="inlineStr">
+      <c r="BE4" t="inlineStr">
         <is>
           <t>https://www.expedientepublico.org/el-salvador-y-china-megaobras-entre-secretismo-y-dano-ambiental/</t>
         </is>
       </c>
-      <c r="BD4" t="inlineStr">
+      <c r="BF4" t="inlineStr">
         <is>
           <t>https://es-us.noticias.yahoo.com/deportes/millonarias-obras-financiadas-china-salvador-144958591.html</t>
         </is>
@@ -1030,6 +1138,7 @@
           <t>SLV-0004</t>
         </is>
       </c>
+      <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
         <v>4</v>
       </c>
@@ -1048,10 +1157,8 @@
           <t>SLV</t>
         </is>
       </c>
-      <c r="G5" s="1" t="inlineStr">
-        <is>
-          <t>222</t>
-        </is>
+      <c r="G5" t="n">
+        <v>222</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -1102,6 +1209,9 @@
       <c r="R5" t="n">
         <v>40</v>
       </c>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr"/>
       <c r="V5" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -1117,20 +1227,50 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="inlineStr"/>
+      <c r="AA5" t="inlineStr"/>
+      <c r="AB5" t="inlineStr"/>
+      <c r="AC5" t="inlineStr"/>
+      <c r="AD5" t="inlineStr"/>
+      <c r="AE5" t="inlineStr"/>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="inlineStr"/>
+      <c r="AH5" t="inlineStr"/>
+      <c r="AI5" t="inlineStr"/>
+      <c r="AJ5" t="inlineStr"/>
+      <c r="AK5" t="inlineStr"/>
+      <c r="AL5" t="inlineStr"/>
+      <c r="AM5" t="inlineStr"/>
+      <c r="AN5" t="inlineStr"/>
+      <c r="AO5" t="inlineStr"/>
+      <c r="AP5" t="inlineStr"/>
+      <c r="AQ5" t="inlineStr"/>
+      <c r="AR5" t="inlineStr"/>
+      <c r="AS5" t="inlineStr"/>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AU5" t="inlineStr"/>
+      <c r="AV5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr"/>
+      <c r="AX5" t="inlineStr"/>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr"/>
       <c r="BA5" t="n">
         <v>4</v>
       </c>
-      <c r="BB5" t="inlineStr">
+      <c r="BB5" t="inlineStr"/>
+      <c r="BC5" t="inlineStr"/>
+      <c r="BD5" t="inlineStr">
         <is>
           <t>https://www.elsalvador.com/dinero-y-negocios/entorno-economico/china-el-salvador-cifco-estadios-de-futbol-planta-potabilizadora-ilopango/1276474/2026/</t>
         </is>
       </c>
-      <c r="BC5" t="inlineStr">
+      <c r="BE5" t="inlineStr">
         <is>
           <t>https://diariolahuella.com/china-sigue-dejando-huella-en-el-salvador-con-megaproyectos-historicos/</t>
         </is>
       </c>
-      <c r="BD5" t="inlineStr">
+      <c r="BF5" t="inlineStr">
         <is>
           <t>https://www.expedientepublico.org/el-salvador-y-china-megaobras-entre-secretismo-y-dano-ambiental/</t>
         </is>
@@ -1142,6 +1282,7 @@
           <t>SLV-0005</t>
         </is>
       </c>
+      <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
         <v>5</v>
       </c>
@@ -1160,10 +1301,8 @@
           <t>SLV</t>
         </is>
       </c>
-      <c r="G6" s="1" t="inlineStr">
-        <is>
-          <t>222</t>
-        </is>
+      <c r="G6" t="n">
+        <v>222</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -1214,6 +1353,9 @@
       <c r="R6" t="n">
         <v>100</v>
       </c>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr"/>
       <c r="V6" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -1229,20 +1371,50 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y6" t="inlineStr"/>
+      <c r="Z6" t="inlineStr"/>
+      <c r="AA6" t="inlineStr"/>
+      <c r="AB6" t="inlineStr"/>
+      <c r="AC6" t="inlineStr"/>
+      <c r="AD6" t="inlineStr"/>
+      <c r="AE6" t="inlineStr"/>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="inlineStr"/>
+      <c r="AH6" t="inlineStr"/>
+      <c r="AI6" t="inlineStr"/>
+      <c r="AJ6" t="inlineStr"/>
+      <c r="AK6" t="inlineStr"/>
+      <c r="AL6" t="inlineStr"/>
+      <c r="AM6" t="inlineStr"/>
+      <c r="AN6" t="inlineStr"/>
+      <c r="AO6" t="inlineStr"/>
+      <c r="AP6" t="inlineStr"/>
+      <c r="AQ6" t="inlineStr"/>
+      <c r="AR6" t="inlineStr"/>
+      <c r="AS6" t="inlineStr"/>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AU6" t="inlineStr"/>
+      <c r="AV6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr"/>
+      <c r="AX6" t="inlineStr"/>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr"/>
       <c r="BA6" t="n">
         <v>5</v>
       </c>
-      <c r="BB6" t="inlineStr">
+      <c r="BB6" t="inlineStr"/>
+      <c r="BC6" t="inlineStr"/>
+      <c r="BD6" t="inlineStr">
         <is>
           <t>https://www.revistaeyn.com/centroamericaymundo/este-sera-el-nuevo-estadio-nacional-de-el-salvador-donado-por-china-MF16467946</t>
         </is>
       </c>
-      <c r="BC6" t="inlineStr">
+      <c r="BE6" t="inlineStr">
         <is>
           <t>https://diario.elmundo.sv/politica/bukele-y-embajador-chino-colocan-primera-piedra-del-estadio-nacional</t>
         </is>
       </c>
-      <c r="BD6" t="inlineStr">
+      <c r="BF6" t="inlineStr">
         <is>
           <t>https://www.elimparcial.com/deporte/2025/12/23/el-salvador-tendra-un-mejor-estadio-que-el-azteca-en-2027-china-financia-el-megaproyecto-con-100-millones-de-dolares/</t>
         </is>
@@ -1254,6 +1426,7 @@
           <t>SLV-0006</t>
         </is>
       </c>
+      <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
         <v>6</v>
       </c>
@@ -1272,10 +1445,8 @@
           <t>SLV</t>
         </is>
       </c>
-      <c r="G7" s="1" t="inlineStr">
-        <is>
-          <t>222</t>
-        </is>
+      <c r="G7" t="n">
+        <v>222</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -1326,6 +1497,9 @@
       <c r="R7" t="n">
         <v>54</v>
       </c>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr"/>
       <c r="V7" t="inlineStr">
         <is>
           <t>Construcción</t>
@@ -1341,20 +1515,50 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="Y7" t="inlineStr"/>
+      <c r="Z7" t="inlineStr"/>
+      <c r="AA7" t="inlineStr"/>
+      <c r="AB7" t="inlineStr"/>
+      <c r="AC7" t="inlineStr"/>
+      <c r="AD7" t="inlineStr"/>
+      <c r="AE7" t="inlineStr"/>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="inlineStr"/>
+      <c r="AH7" t="inlineStr"/>
+      <c r="AI7" t="inlineStr"/>
+      <c r="AJ7" t="inlineStr"/>
+      <c r="AK7" t="inlineStr"/>
+      <c r="AL7" t="inlineStr"/>
+      <c r="AM7" t="inlineStr"/>
+      <c r="AN7" t="inlineStr"/>
+      <c r="AO7" t="inlineStr"/>
+      <c r="AP7" t="inlineStr"/>
+      <c r="AQ7" t="inlineStr"/>
+      <c r="AR7" t="inlineStr"/>
+      <c r="AS7" t="inlineStr"/>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AU7" t="inlineStr"/>
+      <c r="AV7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr"/>
+      <c r="AX7" t="inlineStr"/>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr"/>
       <c r="BA7" t="n">
         <v>5</v>
       </c>
-      <c r="BB7" t="inlineStr">
+      <c r="BB7" t="inlineStr"/>
+      <c r="BC7" t="inlineStr"/>
+      <c r="BD7" t="inlineStr">
         <is>
           <t>https://es-us.noticias.yahoo.com/deportes/millonarias-obras-financiadas-china-salvador-144958591.html</t>
         </is>
       </c>
-      <c r="BC7" t="inlineStr">
+      <c r="BE7" t="inlineStr">
         <is>
           <t>https://archivo.tiempo.hn/impresionante-asi-sera-la-biblioteca-nacional-de-el-salvador-construida-por-china/</t>
         </is>
       </c>
-      <c r="BD7" t="inlineStr">
+      <c r="BF7" t="inlineStr">
         <is>
           <t>https://nicasnews.com/2021/nueva-biblioteca-nacional-binaes/</t>
         </is>

--- a/data/sources/countries/el_salvador.xlsx
+++ b/data/sources/countries/el_salvador.xlsx
@@ -916,7 +916,7 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>30 MW photovoltaic plant and new 34.5/115 kV substation: design, construction, supply, installation, testing and commissioning. First direct Chinese participation in Salvadoran power generation infrastructure.</t>
+          <t>30 MW photovoltaic plant and new 34.5/115 kV substation: design, construction, supply, installation,</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
@@ -1054,7 +1054,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Tourist pier at the Port of La Libertad, with seafront restaurants, part of the Surf City project; built by CHEC and inaugurated in November 2024.</t>
+          <t>Tourist pier at the Port of La Libertad, with seafront restaurants, part of the Surf City project; built by CHEC and.</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
